--- a/1_Data/Smith_2024_Cortex/Codebook_Smith_2024_Cortex_Exp1_Clean.xlsx
+++ b/1_Data/Smith_2024_Cortex/Codebook_Smith_2024_Cortex_Exp1_Clean.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t xml:space="preserve">Variable_name</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t xml:space="preserve">1;0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stranger;Close;Self</t>
   </si>
 </sst>
 </file>
@@ -632,7 +635,7 @@
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -646,7 +649,7 @@
         <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
@@ -660,7 +663,7 @@
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
